--- a/China NEA/review_workbooks/2025-04-29_2025年一季度光伏发电建设情况---国家能源局_review.xlsx
+++ b/China NEA/review_workbooks/2025-04-29_2025年一季度光伏发电建设情况---国家能源局_review.xlsx
@@ -428,1913 +428,999 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
       <c r="B1" t="n">
-        <v>0</v>
+        <v>5971</v>
       </c>
       <c r="C1" t="n">
-        <v>1</v>
+        <v>2341</v>
       </c>
       <c r="D1" t="n">
+        <v>3631</v>
+      </c>
+      <c r="E1" t="n">
+        <v>505</v>
+      </c>
+      <c r="F1" t="n">
+        <v>94544</v>
+      </c>
+      <c r="G1" t="n">
+        <v>53440</v>
+      </c>
+      <c r="H1" t="n">
+        <v>41104</v>
+      </c>
+      <c r="I1" t="n">
+        <v>15032</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>140.7</v>
+      </c>
+      <c r="I2" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>790.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>380.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>219.3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7435</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4425.6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3009.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1902.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3769.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2692.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1076.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>616.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4853.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4531.9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>321.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>144.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1264.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>550.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>714.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>374.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>吉林</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>616.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>392.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>223.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>747.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>481.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>444.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>401.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>666.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>197.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>468.7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6831.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1793.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5038.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1829.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>浙江</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>343.8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>331.1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5071.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>846.6</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4224.6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>529.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>373.4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>322</v>
+      </c>
+      <c r="E13" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4684.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1493.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3191.4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1348.9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1262.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>400.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="C15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2624.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1375.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1249.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>676.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>450.9</v>
+      </c>
+      <c r="C16" t="n">
+        <v>175.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>275.6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8064.3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2768.2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5296.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2783.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>224.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>197.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4573.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>656.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3916.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2329.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>269.4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>266.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3779.3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2150.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1629</v>
+      </c>
+      <c r="I18" t="n">
+        <v>325.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>209.6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>192.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2083</v>
+      </c>
+      <c r="G19" t="n">
+        <v>503.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1579.6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>351.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>563.7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>495.2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4679.3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1441.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3237.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>367.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>263.9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>216.3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2316.1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1135.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1180.9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>海南</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>776</v>
+      </c>
+      <c r="G22" t="n">
+        <v>495.4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="C23" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D23" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>352.7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>237.2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>152.7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="E24" t="n">
         <v>2</v>
       </c>
-      <c r="E1" t="n">
+      <c r="F24" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G24" t="n">
+        <v>946.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2106.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1969.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="I25" t="n">
         <v>3</v>
       </c>
-      <c r="F1" t="n">
-        <v>4</v>
-      </c>
-      <c r="G1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J1" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>省（区、市）</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2025年一季度新增并网容量
-其中：
-其中：分布式光伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2025年一季度新增并网容量
-其中：
-其中：分布式光伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2025年一季度新增并网容量
-其中：
-其中：分布式光伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2025年一季度新增并网容量
-其中：
-其中：分布式光伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>截至2025年3月底累计并网容量
-其中：
-其中：分布式光伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>截至2025年3月底累计并网容量
-其中：
-其中：分布式光伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>截至2025年3月底累计并网容量
-其中：
-其中：分布式光伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>截至2025年3月底累计并网容量
-其中：
-其中：分布式光伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>省（区、市）</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2025年一季度新增并网容量
-其中：
-其中：分布式光伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>其中：
-集中式
-光伏电</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏
-其中：</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏
-其中：</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>截至2025年3月底累计并网容量
-其中：
-其中：分布式光伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>其中：
-集中式
-光伏电</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏
-其中：</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏
-其中：</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>省（区、市）</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2025年一季度新增并网容量
-其中：
-其中：分布式光伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>其中：
-集中式
-光伏电</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏
-其中：</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>其中：</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>截至2025年3月底累计并网容量
-其中：
-其中：分布式光伏
-集中式
-其中：
-光伏电</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>其中：
-集中式
-光伏电</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>其中：分布式光伏
-其中：</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>其中：</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>516.9</v>
+      </c>
+      <c r="C26" t="n">
+        <v>482.8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4239.9</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3915.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>324.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>36.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>497.4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>492</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3561.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2563.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>997.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>452.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="C29" t="n">
+        <v>55</v>
+      </c>
+      <c r="D29" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E29" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>站</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>户用</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>站</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>户用</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>光伏</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>光伏</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5971</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2341</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>3631</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>94544</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>53440</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>41104</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>15032</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>148.8</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>140.7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>天津</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>66.3</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>29.4</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>790.4</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>380.7</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>409.8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>47.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>219.3</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>118.2</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>101.1</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>14.4</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>7435.0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4425.6</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3009.5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1902.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>292.5</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>191.9</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>100.6</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3769.4</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2692.9</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1076.5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>616.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4853.6</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4531.9</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>321.7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>144.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>42.6</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>1264.6</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>550.1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>714.5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>374.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>33.5</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>22.7</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>616.5</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>392.7</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>223.7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>126.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>黑龙江</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>747.7</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>481.1</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>266.6</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>69.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>30.1</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>444.1</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>42.3</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>401.8</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>23.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>666.6</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>197.9</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>468.7</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>128.1</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>6831.4</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1793.1</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5038.4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>1829.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>343.8</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>12.7</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>331.1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>5071.3</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>846.6</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4224.6</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>529.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>373.4</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>322.0</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>83.5</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>4684.8</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1493.4</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3191.4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>1433.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>90.6</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>80.4</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1348.9</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>86.7</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1262.2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>400.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>74.1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2624.5</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>1375.5</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1249.1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>676.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>450.9</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>175.3</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>275.6</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>20.2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>8064.3</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2768.2</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5296.1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2783.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>224.5</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>197.7</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>4573.6</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>656.8</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3916.9</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2329.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>269.4</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>266.9</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>3779.3</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2150.3</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1629.0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>325.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>209.6</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>192.3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2083.0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>503.4</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1579.6</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>351.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>563.7</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>68.6</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>495.2</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>25.4</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>4679.3</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1441.8</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3237.5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>367.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>263.9</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>216.3</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2316.1</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1135.3</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1180.9</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>海南</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>35.2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>776.0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>495.4</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>280.6</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>25.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>34.6</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>352.7</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>115.5</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>237.2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
+      <c r="F29" t="n">
+        <v>3214.4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3009.9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>204.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>152.7</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>57.2</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>95.4</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1235.0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>946.5</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>288.5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>25.9</t>
-        </is>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3671.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3630.9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.4</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>120.6</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>93.7</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>26.9</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2106.2</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>1969.7</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>宁夏</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="C31" t="n">
+        <v>130</v>
+      </c>
+      <c r="D31" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2769.7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2579.3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>190.4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>18.7</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>516.9</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>482.8</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>34.1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>4239.9</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>3915.8</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>324.1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>36.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>西藏</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>83.6</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>83.6</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>497.4</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>492.0</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>128.2</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>88.5</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>3561.1</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2563.5</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>997.5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>452.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>甘肃</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>75.6</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>3214.4</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>3009.9</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>204.5</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>青海</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>29.4</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>3671.5</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>3630.9</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>40.6</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>宁夏</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>145.7</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>15.7</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2769.7</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2579.3</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>190.4</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>新疆</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>323.5</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>321.8</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>5993.2</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>5964.7</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>28.5</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>3.9</t>
-        </is>
+      <c r="B32" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>321.8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5993.2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5964.7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3.9</v>
       </c>
     </row>
   </sheetData>
@@ -2382,11 +1468,7 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>省（区、市）</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>省(区、市)</t>
@@ -2407,11 +1489,7 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025年一季度新增并网容量其中：其中：分布式光伏集中式其中：光伏电</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>2025年一季度新增并网容量</t>
@@ -2432,11 +1510,7 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025年一季度新增并网容量其中：其中：分布式光伏集中式其中：光伏电其中：集中式光伏电站</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>2025年一季度新增并网容量_其中：集中式光伏电站</t>
@@ -2457,11 +1531,7 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2025年一季度新增并网容量其中：其中：分布式光伏集中式其中：光伏电其中：分布式光伏其中：</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>2025年一季度新增并网容量_其中：分布式光伏</t>
@@ -2482,11 +1552,7 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2025年一季度新增并网容量其中：其中：分布式光伏集中式其中：光伏电其中：分布式光伏其中：其中：户用光伏</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>2025年一季度新增并网容量_其中：户用光伏</t>
@@ -2507,11 +1573,7 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>截至2025年3月底累计并网容量其中：其中：分布式光伏集中式其中：光伏电</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>截至2025年3月底累计并网容量</t>
@@ -2532,11 +1594,7 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>截至2025年3月底累计并网容量其中：其中：分布式光伏集中式其中：光伏电其中：集中式光伏电站</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>截至2025年3月底累计并网容量_其中：集中式光伏电站</t>
@@ -2557,11 +1615,7 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>截至2025年3月底累计并网容量其中：其中：分布式光伏集中式其中：光伏电其中：分布式光伏其中：</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>截至2025年3月底累计并网容量_其中：分布式光伏</t>
@@ -2582,11 +1636,7 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>截至2025年3月底累计并网容量其中：其中：分布式光伏集中式其中：光伏电其中：分布式光伏其中：其中：户用光伏</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>截至2025年3月底累计并网容量_其中：户用光伏</t>
